--- a/conference_registration_forms/016_healthcare_workforce_inclusion_forum_registration--conference_registration_forms.xlsx
+++ b/conference_registration_forms/016_healthcare_workforce_inclusion_forum_registration--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'first_name':_'john_doe'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'First name': 'John Doe'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'last_name':_'jane_doe'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Last name': 'Jane Doe'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'organization':_'example_organization'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Organization': 'Example Organization'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'title':_'event_coordinator'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'Title': 'Event Coordinator'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'job_title':_'registration_manager'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'Job Title': 'Registration Manager'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'department':_'registration_and_events'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'Department': 'Registration and Events'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'email':_'jimmy@example.com'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'Email': 'jimmy@example.com'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'phone':_'123-456-7890'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'Phone': '123-456-7890'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'role':_'event_staff'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'Role': 'Event Staff'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'position':_'manager'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'Position': 'Manager'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'status':_'registered'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'Status': 'Registered'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'time':_720}</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'Time': 720}</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'timezone':_'america/new_york'}</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'Timezone': 'America/New York'}</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'city':_'new_york'}</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'City': 'New York'}</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'address':_'123_main_st'}</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'Address': '123 Main St'}</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'state':_'ny'}</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'State': 'NY'}</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'zip':_10001}</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'Zip': 10001}</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>america/new_york</t>
+          <t>america/detroit</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>America/New York</t>
+          <t>America/Detroit</t>
         </is>
       </c>
     </row>
@@ -1361,46 +1361,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>america/detroit</t>
+          <t>america/indianapolis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>America/Detroit</t>
+          <t>America/Indianapolis</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>confirm_timezone_choices</t>
+          <t>confirm_state_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>America/Indianapolis</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>confirm_timezone_choices</t>
+          <t>confirm_state_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>america/indianapolis</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>America/Indianapolis</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>california</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>illinois</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>texas</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>florida</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1497,44 +1497,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ohio</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>confirm_state_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>michigan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>confirm_state_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>new_jersey</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
         <is>
           <t>New Jersey</t>
         </is>
